--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484544_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484544_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.0894</v>
+        <v>6.0597</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4408</v>
+        <v>4.2625</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6486</v>
+        <v>1.7972</v>
       </c>
       <c r="G2" t="n">
         <v>3.7993</v>
@@ -610,13 +610,13 @@
         <v>2.9321</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3775</v>
+        <v>-0.4072</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8401999999999999</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.2177</v>
+        <v>-1.069</v>
       </c>
       <c r="V2" t="n">
         <v>1.5681</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. SORO VILLANUEVA</t>
+          <t>F. ROMAN MORA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9673</v>
+        <v>3.2806</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0513</v>
+        <v>1.8309</v>
       </c>
       <c r="F3" t="n">
-        <v>0.916</v>
+        <v>1.4498</v>
       </c>
       <c r="G3" t="n">
-        <v>6.1589</v>
+        <v>1.8591</v>
       </c>
       <c r="H3" t="n">
-        <v>4.1232</v>
+        <v>1.7662</v>
       </c>
       <c r="I3" t="n">
-        <v>2.0357</v>
+        <v>0.0929</v>
       </c>
       <c r="J3" t="n">
-        <v>6.9652</v>
+        <v>1.5647</v>
       </c>
       <c r="K3" t="n">
-        <v>4.2882</v>
+        <v>1.4397</v>
       </c>
       <c r="L3" t="n">
-        <v>2.677</v>
+        <v>0.125</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8063</v>
+        <v>0.2944</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.165</v>
+        <v>0.3265</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6413</v>
+        <v>-0.0321</v>
       </c>
       <c r="P3" t="n">
-        <v>-4.0317</v>
+        <v>1.2828</v>
       </c>
       <c r="Q3" t="n">
-        <v>-6.5973</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.5656</v>
+        <v>1.2828</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8401</v>
+        <v>-0.1833</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6833</v>
+        <v>-0.0558</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8431999999999999</v>
+        <v>-0.1275</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8802</v>
+        <v>2.2589</v>
       </c>
       <c r="E4" t="n">
-        <v>4.3003</v>
+        <v>4.0258</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.4201</v>
+        <v>-1.7669</v>
       </c>
       <c r="G4" t="n">
         <v>4.1597</v>
@@ -766,13 +766,13 @@
         <v>1.4661</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8879</v>
+        <v>0.2666</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7866</v>
+        <v>0.5121</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1013</v>
+        <v>-0.2455</v>
       </c>
       <c r="V4" t="n">
         <v>-2.5339</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. ROMAN MORA</t>
+          <t>E. NAVARRO VALDÉS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6978</v>
+        <v>2.2256</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4463</v>
+        <v>2.2256</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2516</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8591</v>
+        <v>2.2256</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7662</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0929</v>
+        <v>1.2502</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5647</v>
+        <v>2.2256</v>
       </c>
       <c r="K5" t="n">
-        <v>1.4397</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>0.125</v>
+        <v>1.2502</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2944</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3265</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0321</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.2828</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2828</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7661</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4404</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3256</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. NAVARRO VALDES</t>
+          <t>R. SORO VILLANUEVA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.5536</v>
+        <v>2.0999</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8922</v>
+        <v>0.9114</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6614</v>
+        <v>1.1885</v>
       </c>
       <c r="G6" t="n">
-        <v>2.6208</v>
+        <v>6.1589</v>
       </c>
       <c r="H6" t="n">
-        <v>3.502</v>
+        <v>4.1232</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8812</v>
+        <v>2.0357</v>
       </c>
       <c r="J6" t="n">
-        <v>3.2777</v>
+        <v>6.9652</v>
       </c>
       <c r="K6" t="n">
-        <v>3.774</v>
+        <v>4.2882</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.4963</v>
+        <v>2.677</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6569</v>
+        <v>-0.8063</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2719</v>
+        <v>-0.165</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3849</v>
+        <v>-0.6413</v>
       </c>
       <c r="P6" t="n">
-        <v>-0</v>
+        <v>-4.0317</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.9321</v>
+        <v>-6.5973</v>
       </c>
       <c r="R6" t="n">
-        <v>2.9321</v>
+        <v>2.5656</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5663</v>
+        <v>-0.0273</v>
       </c>
       <c r="T6" t="n">
-        <v>1.5362</v>
+        <v>0.5434</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.9699</v>
+        <v>-0.5707</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6335</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0104</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. NAVARRO VALDÉS</t>
+          <t>E. NAVARRO VALDES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.2256</v>
+        <v>1.8781</v>
       </c>
       <c r="E7" t="n">
-        <v>2.2256</v>
+        <v>1.192</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>0.6862</v>
       </c>
       <c r="G7" t="n">
-        <v>2.2256</v>
+        <v>2.6208</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9752999999999999</v>
+        <v>3.502</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2502</v>
+        <v>-0.8812</v>
       </c>
       <c r="J7" t="n">
-        <v>2.2256</v>
+        <v>3.2777</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9752999999999999</v>
+        <v>3.774</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2502</v>
+        <v>-0.4963</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-0.6569</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-0.2719</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-0.3849</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.9321</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.9321</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0.1092</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.836</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0.9452</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.6335</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.0104</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. SALVADOR MONTAÑES</t>
+          <t>A. ALVAREZ LENCINA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2753</v>
+        <v>1.834</v>
       </c>
       <c r="E8" t="n">
-        <v>1.2753</v>
+        <v>1.0474</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>0.7866</v>
       </c>
       <c r="G8" t="n">
-        <v>1.2753</v>
+        <v>-0.0631</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6502</v>
+        <v>0.3247</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6251</v>
+        <v>-0.3878</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2753</v>
+        <v>0.3966</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6502</v>
+        <v>0.3034</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6251</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>-0.4597</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>0.0213</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>-0.481</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.8326</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.8326</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>0.0645</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.3288</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>-0.2643</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. ALVAREZ LENCINA</t>
+          <t>L. SALVADOR MONTAÑES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1583</v>
+        <v>1.2753</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2231</v>
+        <v>1.2753</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9352</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0631</v>
+        <v>1.2753</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3247</v>
+        <v>0.6502</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3878</v>
+        <v>0.6251</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3966</v>
+        <v>1.2753</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3034</v>
+        <v>0.6502</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09320000000000001</v>
+        <v>0.6251</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4597</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0213</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.481</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.8326</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8326</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6112</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4955</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1157</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7302</v>
+        <v>0.7487</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7782</v>
+        <v>-0.3385</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5083</v>
+        <v>1.0872</v>
       </c>
       <c r="G10" t="n">
         <v>-0.5953000000000001</v>
@@ -1234,13 +1234,13 @@
         <v>1.4661</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4625</v>
+        <v>-0.444</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5875</v>
+        <v>-0.1478</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1249</v>
+        <v>-0.2962</v>
       </c>
       <c r="V10" t="n">
         <v>0.3219</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.1587</v>
+        <v>-0.8702</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1855</v>
+        <v>-1.8971</v>
       </c>
       <c r="F11" t="n">
         <v>1.0268</v>
@@ -1312,10 +1312,10 @@
         <v>1.2828</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4027</v>
+        <v>-0.1143</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2202</v>
+        <v>0.0683</v>
       </c>
       <c r="U11" t="n">
         <v>-0.1825</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.7511</v>
+        <v>-2.3326</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.1292</v>
+        <v>-3.0575</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3781</v>
+        <v>0.7249</v>
       </c>
       <c r="G12" t="n">
         <v>-1.0503</v>
@@ -1390,13 +1390,13 @@
         <v>2.3823</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.8578</v>
+        <v>-0.4393</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8077</v>
+        <v>0.264</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.0501</v>
+        <v>-0.7033</v>
       </c>
       <c r="V12" t="n">
         <v>0.6231</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.5864</v>
+        <v>-5.5506</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.6521</v>
+        <v>-6.542</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0657</v>
+        <v>0.9913999999999999</v>
       </c>
       <c r="G13" t="n">
         <v>-6.5354</v>
@@ -1468,13 +1468,13 @@
         <v>2.9321</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5616</v>
+        <v>-0.5258</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2542</v>
+        <v>0.3643</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.8158</v>
+        <v>-0.8901</v>
       </c>
       <c r="V13" t="n">
         <v>-0.3219</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>12.08149999999999</v>
+        <v>12.9074</v>
       </c>
       <c r="E14" t="n">
-        <v>4.109900000000001</v>
+        <v>4.935799999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>7.9716</v>
+        <v>7.971699999999999</v>
       </c>
       <c r="G14" t="n">
         <v>13.3552</v>
@@ -1519,7 +1519,7 @@
         <v>-3.2052</v>
       </c>
       <c r="J14" t="n">
-        <v>16.3657</v>
+        <v>16.36570000000001</v>
       </c>
       <c r="K14" t="n">
         <v>16.04299999999999</v>
@@ -1531,7 +1531,7 @@
         <v>-3.0106</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5173999999999999</v>
+        <v>0.5174000000000001</v>
       </c>
       <c r="O14" t="n">
         <v>-3.5279</v>
@@ -1546,13 +1546,13 @@
         <v>21.0746</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.7451</v>
+        <v>-1.9193</v>
       </c>
       <c r="T14" t="n">
-        <v>2.5492</v>
+        <v>3.3751</v>
       </c>
       <c r="U14" t="n">
-        <v>-5.294300000000001</v>
+        <v>-5.2943</v>
       </c>
       <c r="V14" t="n">
         <v>-1.2774</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.1246</v>
+        <v>3.6152</v>
       </c>
       <c r="E15" t="n">
-        <v>5.1239</v>
+        <v>3.5854</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0007</v>
+        <v>0.0298</v>
       </c>
       <c r="G15" t="n">
         <v>2.8098</v>
@@ -1624,13 +1624,13 @@
         <v>2.1991</v>
       </c>
       <c r="S15" t="n">
-        <v>2.8646</v>
+        <v>1.3552</v>
       </c>
       <c r="T15" t="n">
-        <v>2.9653</v>
+        <v>1.4269</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1008</v>
+        <v>-0.0717</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3497</v>
+        <v>1.0147</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3348</v>
+        <v>1.9501</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.985</v>
+        <v>-0.9355</v>
       </c>
       <c r="G16" t="n">
         <v>-1.481</v>
@@ -1702,13 +1702,13 @@
         <v>1.2828</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5821</v>
+        <v>0.247</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7677</v>
+        <v>0.3831</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1857</v>
+        <v>-0.1361</v>
       </c>
       <c r="V16" t="n">
         <v>0.9658</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.081</v>
+        <v>0.628</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7368</v>
+        <v>1.1598</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6556999999999999</v>
+        <v>-0.5319</v>
       </c>
       <c r="G17" t="n">
         <v>-0.4118</v>
@@ -1780,13 +1780,13 @@
         <v>0.9163</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5766</v>
+        <v>0.1235</v>
       </c>
       <c r="T17" t="n">
-        <v>0.9517</v>
+        <v>0.3748</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3752</v>
+        <v>-0.2513</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.143</v>
+        <v>0.3396</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6097</v>
+        <v>-0.4174</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7527</v>
+        <v>0.757</v>
       </c>
       <c r="G18" t="n">
         <v>-0.626</v>
@@ -1858,13 +1858,13 @@
         <v>1.0995</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3201</v>
+        <v>-0.1235</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2021</v>
+        <v>-0.0098</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.118</v>
+        <v>-0.1137</v>
       </c>
       <c r="V18" t="n">
         <v>-0.0104</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. CARPIO MANEZ</t>
+          <t>M. CISNEROS RUIZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3673</v>
+        <v>-0.0446</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9433</v>
+        <v>0.9696</v>
       </c>
       <c r="F19" t="n">
-        <v>0.576</v>
+        <v>-1.0142</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3519</v>
+        <v>-0.3638</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0327</v>
+        <v>0.2454</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3846</v>
+        <v>-0.6092</v>
       </c>
       <c r="J19" t="n">
-        <v>0.065</v>
+        <v>0.7369</v>
       </c>
       <c r="K19" t="n">
-        <v>0.065</v>
+        <v>0.7369</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2869</v>
+        <v>-1.1008</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0977</v>
+        <v>-0.4916</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3846</v>
+        <v>-0.6092</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.5498</v>
+        <v>0.9163</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3665</v>
+        <v>0.9163</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1526</v>
+        <v>-0.2751</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.092</v>
+        <v>0.2327</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2446</v>
+        <v>-0.5077</v>
       </c>
       <c r="V19" t="n">
         <v>-0.3219</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. HORTELANO ESCRIBA</t>
+          <t>J. CARPIO MANEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5799</v>
+        <v>-0.2493</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0971</v>
+        <v>-0.751</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5172</v>
+        <v>0.5017</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.6957</v>
+        <v>0.3519</v>
       </c>
       <c r="H20" t="n">
-        <v>-4.6187</v>
+        <v>-0.0327</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.077</v>
+        <v>0.3846</v>
       </c>
       <c r="J20" t="n">
-        <v>-4.3611</v>
+        <v>0.065</v>
       </c>
       <c r="K20" t="n">
-        <v>-3.1624</v>
+        <v>0.065</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.1987</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3345</v>
+        <v>0.2869</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.4563</v>
+        <v>-0.0977</v>
       </c>
       <c r="O20" t="n">
-        <v>1.1217</v>
+        <v>0.3846</v>
       </c>
       <c r="P20" t="n">
-        <v>1.2828</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1991</v>
+        <v>0.3665</v>
       </c>
       <c r="S20" t="n">
-        <v>1.566</v>
+        <v>0.2705</v>
       </c>
       <c r="T20" t="n">
-        <v>1.6463</v>
+        <v>0.1003</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0803</v>
+        <v>0.1702</v>
       </c>
       <c r="V20" t="n">
-        <v>1.267</v>
+        <v>-0.3219</v>
       </c>
       <c r="W20" t="n">
-        <v>2.5339</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.267</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. CARRION BALLESTER</t>
+          <t>S. CARRION BALLESTER</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5992</v>
+        <v>-0.2589</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3884</v>
+        <v>-0.4637</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2107</v>
+        <v>0.2047</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.1556</v>
+        <v>1.2955</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4118</v>
+        <v>-1.8621</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.5674</v>
+        <v>3.1577</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9403</v>
+        <v>3.323</v>
       </c>
       <c r="K21" t="n">
-        <v>2.155</v>
+        <v>0.0368</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.2146</v>
+        <v>3.2862</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.0959</v>
+        <v>-2.0275</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.7431</v>
+        <v>-1.899</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3528</v>
+        <v>-0.1285</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.3665</v>
+        <v>-1.2828</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.8326</v>
+        <v>-3.6651</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4661</v>
+        <v>2.3823</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2894</v>
+        <v>0.3618</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1297</v>
+        <v>0.5014999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4191</v>
+        <v>-0.1397</v>
       </c>
       <c r="V21" t="n">
-        <v>0.6335</v>
+        <v>-0.6335</v>
       </c>
       <c r="W21" t="n">
-        <v>0.6335</v>
+        <v>-0.6231</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.0104</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. CISNEROS RUIZ</t>
+          <t>A. CARRION BALLESTER</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.8415</v>
+        <v>-0.5089</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2965</v>
+        <v>-0.1</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.138</v>
+        <v>-0.4089</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3638</v>
+        <v>-1.1556</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2454</v>
+        <v>0.4118</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6092</v>
+        <v>-1.5674</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7369</v>
+        <v>0.9403</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7369</v>
+        <v>2.155</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>-1.2146</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.1008</v>
+        <v>-2.0959</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4916</v>
+        <v>-1.7431</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6092</v>
+        <v>-0.3528</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9163</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9163</v>
+        <v>1.4661</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.072</v>
+        <v>0.3797</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4404</v>
+        <v>0.1588</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6316000000000001</v>
+        <v>0.221</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.3219</v>
+        <v>0.6335</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.6335</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S. CARRION BALLESTER</t>
+          <t>C. HORTELANO ESCRIBA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.8572</v>
+        <v>-1.4409</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.8098</v>
+        <v>-1.9625</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0473</v>
+        <v>0.5216</v>
       </c>
       <c r="G23" t="n">
-        <v>1.2955</v>
+        <v>-4.6957</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.8621</v>
+        <v>-4.6187</v>
       </c>
       <c r="I23" t="n">
-        <v>3.1577</v>
+        <v>-0.077</v>
       </c>
       <c r="J23" t="n">
-        <v>3.323</v>
+        <v>-4.3611</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0368</v>
+        <v>-3.1624</v>
       </c>
       <c r="L23" t="n">
-        <v>3.2862</v>
+        <v>-1.1987</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.0275</v>
+        <v>-0.3345</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.899</v>
+        <v>-1.4563</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.1285</v>
+        <v>1.1217</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.2828</v>
+        <v>1.2828</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.6651</v>
+        <v>-0.9163</v>
       </c>
       <c r="R23" t="n">
-        <v>2.3823</v>
+        <v>2.1991</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2364</v>
+        <v>0.7049</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8446</v>
+        <v>0.7809</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3918</v>
+        <v>-0.076</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6335</v>
+        <v>1.267</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.6231</v>
+        <v>2.5339</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.0104</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. GARCIA ZANON</t>
+          <t>F. BLASCO MANZANO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,58 +2281,58 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.2427</v>
+        <v>-3.1213</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.4149</v>
+        <v>-2.282</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1722</v>
+        <v>-0.8391999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.5435</v>
+        <v>-1.2474</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.8352</v>
+        <v>-0.6576</v>
       </c>
       <c r="I24" t="n">
-        <v>2.2918</v>
+        <v>-0.5898</v>
       </c>
       <c r="J24" t="n">
-        <v>0.4734</v>
+        <v>1.2745</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.9852</v>
+        <v>1.223</v>
       </c>
       <c r="L24" t="n">
-        <v>1.4586</v>
+        <v>0.0515</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.0169</v>
+        <v>-2.5219</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.8501</v>
+        <v>-1.8805</v>
       </c>
       <c r="O24" t="n">
-        <v>0.8332000000000001</v>
+        <v>-0.6413</v>
       </c>
       <c r="P24" t="n">
-        <v>-3.2986</v>
+        <v>-1.8326</v>
       </c>
       <c r="Q24" t="n">
-        <v>-5.4977</v>
+        <v>-3.6651</v>
       </c>
       <c r="R24" t="n">
-        <v>2.1991</v>
+        <v>1.8326</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5994</v>
+        <v>-0.0413</v>
       </c>
       <c r="T24" t="n">
-        <v>1.6094</v>
+        <v>0.1086</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.01</v>
+        <v>-0.1499</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>F. BLASCO MANZANO</t>
+          <t>M. GARCIA ZANON</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,58 +2359,58 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.8657</v>
+        <v>-3.3941</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.0513</v>
+        <v>-3.9918</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.8144</v>
+        <v>0.5977</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.2474</v>
+        <v>-0.5435</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.6576</v>
+        <v>-2.8352</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.5898</v>
+        <v>2.2918</v>
       </c>
       <c r="J25" t="n">
-        <v>1.2745</v>
+        <v>0.4734</v>
       </c>
       <c r="K25" t="n">
-        <v>1.223</v>
+        <v>-0.9852</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0515</v>
+        <v>1.4586</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.5219</v>
+        <v>-1.0169</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.8805</v>
+        <v>-1.8501</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.6413</v>
+        <v>0.8332000000000001</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.8326</v>
+        <v>-3.2986</v>
       </c>
       <c r="Q25" t="n">
-        <v>-3.6651</v>
+        <v>-5.4977</v>
       </c>
       <c r="R25" t="n">
-        <v>1.8326</v>
+        <v>2.1991</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7857</v>
+        <v>0.448</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6606</v>
+        <v>1.0325</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1251</v>
+        <v>-0.5845</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-8.426500000000001</v>
+        <v>-8.02</v>
       </c>
       <c r="E26" t="n">
-        <v>-6.149</v>
+        <v>-5.6682</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.2775</v>
+        <v>-2.3518</v>
       </c>
       <c r="G26" t="n">
         <v>-7.2877</v>
@@ -2482,13 +2482,13 @@
         <v>1.4661</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.4711</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.2767</v>
+        <v>0.204</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.1944</v>
+        <v>-0.2687</v>
       </c>
       <c r="V26" t="n">
         <v>-0.3011</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-12.0817</v>
+        <v>-11.4405</v>
       </c>
       <c r="E27" t="n">
-        <v>-7.971499999999999</v>
+        <v>-7.971699999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>-4.1098</v>
+        <v>-3.469</v>
       </c>
       <c r="G27" t="n">
         <v>-13.3553</v>
@@ -2530,7 +2530,7 @@
         <v>-16.5603</v>
       </c>
       <c r="I27" t="n">
-        <v>3.205099999999999</v>
+        <v>3.2051</v>
       </c>
       <c r="J27" t="n">
         <v>3.010399999999999</v>
@@ -2560,13 +2560,13 @@
         <v>18.3258</v>
       </c>
       <c r="S27" t="n">
-        <v>2.745400000000001</v>
+        <v>3.386</v>
       </c>
       <c r="T27" t="n">
         <v>5.2943</v>
       </c>
       <c r="U27" t="n">
-        <v>-2.5492</v>
+        <v>-1.9081</v>
       </c>
       <c r="V27" t="n">
         <v>1.2775</v>
